--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU10/HRM/post FET_HRM-2031-0232/panel_11/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU10_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU10/HRM/post FET_HRM-2031-0232/panel_11/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU10_Back_Summary.xlsx
@@ -413,410 +413,491 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Measured by operator 7 on tool HRM-2</t>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Radius</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Bump</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Max Stepheight</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Min Stepheight</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Mean Stepheight</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Radius</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Pad 1</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>17.68383</v>
+      </c>
+      <c r="D2" t="n">
+        <v>17.51558</v>
+      </c>
+      <c r="E2" t="n">
+        <v>17.54733</v>
+      </c>
+      <c r="F2" t="n">
+        <v>45.0331</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.05328</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.91997</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Pad 1</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.75113</v>
+        <v>17.8413</v>
       </c>
       <c r="D3" t="n">
-        <v>17.18951</v>
+        <v>16.90372</v>
       </c>
       <c r="E3" t="n">
-        <v>17.10722</v>
+        <v>17.17614</v>
       </c>
       <c r="F3" t="n">
-        <v>43.44328</v>
+        <v>44.24003</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05344</v>
+        <v>0.05224</v>
       </c>
       <c r="H3" t="n">
-        <v>1.91416</v>
+        <v>1.8906</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.48705</v>
+        <v>17.88861</v>
       </c>
       <c r="D4" t="n">
-        <v>17.27179</v>
+        <v>17.42428</v>
       </c>
       <c r="E4" t="n">
-        <v>17.12963</v>
+        <v>17.53623</v>
       </c>
       <c r="F4" t="n">
-        <v>43.67292</v>
+        <v>44.32075</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05367</v>
+        <v>0.05296</v>
       </c>
       <c r="H4" t="n">
-        <v>1.89716</v>
+        <v>1.95646</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17.8521</v>
+        <v>17.56977</v>
       </c>
       <c r="D5" t="n">
-        <v>17.10084</v>
+        <v>17.39604</v>
       </c>
       <c r="E5" t="n">
-        <v>17.52229</v>
+        <v>17.40221</v>
       </c>
       <c r="F5" t="n">
-        <v>43.83954</v>
+        <v>44.71778</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05177</v>
+        <v>0.05337</v>
       </c>
       <c r="H5" t="n">
-        <v>1.86685</v>
+        <v>1.91899</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Unit 4</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>17.90661</v>
-      </c>
-      <c r="D6" t="n">
-        <v>17.35709</v>
-      </c>
-      <c r="E6" t="n">
-        <v>17.58042</v>
-      </c>
-      <c r="F6" t="n">
-        <v>45.10003</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.05322</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1.8984</v>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>scratched - not measurable</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.54642</v>
+        <v>17.79312</v>
       </c>
       <c r="D7" t="n">
-        <v>17.13352</v>
+        <v>17.12949</v>
       </c>
       <c r="E7" t="n">
-        <v>17.21073</v>
+        <v>17.44826</v>
       </c>
       <c r="F7" t="n">
-        <v>44.60626</v>
+        <v>44.18005</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05378</v>
+        <v>0.05246</v>
       </c>
       <c r="H7" t="n">
-        <v>1.93086</v>
+        <v>1.94451</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>18.01659</v>
+        <v>17.53125</v>
       </c>
       <c r="D8" t="n">
-        <v>17.57646</v>
+        <v>17.25853</v>
       </c>
       <c r="E8" t="n">
-        <v>17.19671</v>
+        <v>17.37225</v>
       </c>
       <c r="F8" t="n">
-        <v>43.55788</v>
+        <v>44.86153</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05345</v>
+        <v>0.05235</v>
       </c>
       <c r="H8" t="n">
-        <v>1.86934</v>
+        <v>1.85373</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17.52797</v>
+        <v>17.92347</v>
       </c>
       <c r="D9" t="n">
-        <v>16.93048</v>
+        <v>17.2909</v>
       </c>
       <c r="E9" t="n">
-        <v>17.70874</v>
+        <v>17.61881</v>
       </c>
       <c r="F9" t="n">
-        <v>44.42909</v>
+        <v>43.92559</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05213</v>
+        <v>0.05299</v>
       </c>
       <c r="H9" t="n">
-        <v>1.92348</v>
+        <v>1.87026</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17.58859</v>
+        <v>17.7352</v>
       </c>
       <c r="D10" t="n">
-        <v>17.74669</v>
+        <v>17.37629</v>
       </c>
       <c r="E10" t="n">
-        <v>17.90741</v>
+        <v>17.455</v>
       </c>
       <c r="F10" t="n">
-        <v>43.89165</v>
+        <v>45.0943</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05321</v>
+        <v>0.0527</v>
       </c>
       <c r="H10" t="n">
-        <v>1.9214</v>
+        <v>1.91108</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Unit 3</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>17.51972</v>
-      </c>
-      <c r="D11" t="n">
-        <v>17.18472</v>
-      </c>
-      <c r="E11" t="n">
-        <v>17.27269</v>
-      </c>
-      <c r="F11" t="n">
-        <v>45.25015</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.05272</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1.89841</v>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Trace 1</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>17.36668</v>
+      </c>
+      <c r="D12" t="n">
+        <v>16.8309</v>
+      </c>
+      <c r="E12" t="n">
+        <v>17.32972</v>
+      </c>
+      <c r="F12" t="n">
+        <v>22.89656</v>
+      </c>
+      <c r="G12" t="n">
+        <v>35.93532</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>via 1</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.63994</v>
+        <v>17.81001</v>
       </c>
       <c r="D13" t="n">
-        <v>1.1802</v>
+        <v>16.36766</v>
+      </c>
+      <c r="E13" t="n">
+        <v>17.41295</v>
+      </c>
+      <c r="F13" t="n">
+        <v>22.921</v>
+      </c>
+      <c r="G13" t="n">
+        <v>36.14386</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>re-measured</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.63971</v>
+        <v>17.29432</v>
       </c>
       <c r="D14" t="n">
-        <v>1.18766</v>
+        <v>16.38146</v>
+      </c>
+      <c r="E14" t="n">
+        <v>16.75669</v>
+      </c>
+      <c r="F14" t="n">
+        <v>22.98053</v>
+      </c>
+      <c r="G14" t="n">
+        <v>35.94374</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.62566</v>
+        <v>17.3817</v>
       </c>
       <c r="D15" t="n">
-        <v>1.16945</v>
+        <v>16.6399</v>
+      </c>
+      <c r="E15" t="n">
+        <v>16.81818</v>
+      </c>
+      <c r="F15" t="n">
+        <v>22.35637</v>
+      </c>
+      <c r="G15" t="n">
+        <v>36.28362</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.63657</v>
+        <v>17.39063</v>
       </c>
       <c r="D16" t="n">
-        <v>1.17368</v>
+        <v>16.89229</v>
+      </c>
+      <c r="E16" t="n">
+        <v>16.99176</v>
+      </c>
+      <c r="F16" t="n">
+        <v>22.83208</v>
+      </c>
+      <c r="G16" t="n">
+        <v>35.2804</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.64682</v>
+        <v>17.47513</v>
       </c>
       <c r="D17" t="n">
-        <v>1.15832</v>
+        <v>16.38678</v>
+      </c>
+      <c r="E17" t="n">
+        <v>17.08412</v>
+      </c>
+      <c r="F17" t="n">
+        <v>22.75473</v>
+      </c>
+      <c r="G17" t="n">
+        <v>36.01323</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.6322</v>
+        <v>17.71787</v>
       </c>
       <c r="D18" t="n">
-        <v>1.15489</v>
+        <v>16.81651</v>
+      </c>
+      <c r="E18" t="n">
+        <v>17.0856</v>
+      </c>
+      <c r="F18" t="n">
+        <v>22.72578</v>
+      </c>
+      <c r="G18" t="n">
+        <v>35.31177</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.63909</v>
+        <v>17.42441</v>
       </c>
       <c r="D19" t="n">
-        <v>1.16974</v>
+        <v>16.78045</v>
+      </c>
+      <c r="E19" t="n">
+        <v>17.21073</v>
+      </c>
+      <c r="F19" t="n">
+        <v>23.06305</v>
+      </c>
+      <c r="G19" t="n">
+        <v>36.68439</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.63613</v>
+        <v>17.68363</v>
       </c>
       <c r="D20" t="n">
-        <v>1.145</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Unit 3</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>0.6549199999999999</v>
-      </c>
-      <c r="D21" t="n">
-        <v>1.17667</v>
+        <v>16.46715</v>
+      </c>
+      <c r="E20" t="n">
+        <v>16.8009</v>
+      </c>
+      <c r="F20" t="n">
+        <v>22.98385</v>
+      </c>
+      <c r="G20" t="n">
+        <v>35.10198</v>
       </c>
     </row>
   </sheetData>
